--- a/src/test/resources/testdata/Portfolio Planner Test Cases UAT.xlsx
+++ b/src/test/resources/testdata/Portfolio Planner Test Cases UAT.xlsx
@@ -540,10 +540,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -564,8 +560,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Axis Liquid Direct-G</t>
@@ -591,7 +585,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,10 +602,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -633,8 +622,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Axis Liquid Direct-G</t>
@@ -660,7 +647,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -678,10 +664,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -702,8 +684,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Axis Liquid Direct-G</t>
@@ -729,7 +709,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,10 +726,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -771,8 +746,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Axis Liquid Direct-G</t>
@@ -798,7 +771,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -816,10 +788,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -840,8 +808,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Axis Liquid Reg-G</t>
@@ -867,7 +833,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,10 +850,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -909,8 +870,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Nippon India Liquid Direct-G</t>
@@ -936,7 +895,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -954,32 +912,44 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>87681399</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>81843632</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>89659236</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tata Liquid Reg-IDCWD</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=OWFiMzBlMzAtODE5Yi0xMWYwLWJmZWYtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NOT FOUND: 110 Liquid fund plan(s) match 'Good' 4-5 star Regular/Dividend (none AC), and 234 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Tata Liquid Reg-IDCWD bought as one lumpsum of Rs 5,00,000 (2.7% of the account's portfolio) on label 89659236 (Ashutosh Gupta). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -999,32 +969,44 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>87681399</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>81843632</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>89659236</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tata Liquid Reg-IDCWD</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=OWFiMzBlMzAtODE5Yi0xMWYwLWJmZWYtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>NOT FOUND: 110 Liquid fund plan(s) match 'Good' 4-5 star Regular/Dividend (none AC), and 234 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Tata Liquid Reg-IDCWD bought as one lumpsum of Rs 5,00,000 (2.7% of the account's portfolio) on label 89659236 (Ashutosh Gupta). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -1044,32 +1026,19 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Liquid funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Liquid funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Liquid fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -1089,32 +1058,19 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Liquid funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Liquid funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Liquid fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1090,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1158,8 +1110,6 @@
           <t>89658587</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Navi Liquid Direct-G</t>
@@ -1185,7 +1135,6 @@
           <t>Sourav Adhikari</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1203,10 +1152,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1227,8 +1172,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Axis Liquid Direct-G</t>
@@ -1254,7 +1197,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1272,10 +1214,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1296,8 +1234,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Axis Liquid Reg-G</t>
@@ -1323,7 +1259,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1341,10 +1276,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1365,8 +1296,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Nippon India Liquid Direct-G</t>
@@ -1392,7 +1321,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1410,32 +1338,44 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>87681399</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>81843632</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>89659236</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tata Liquid Reg-IDCWD</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=OWFiMzBlMzAtODE5Yi0xMWYwLWJmZWYtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>NOT FOUND: 110 Liquid fund plan(s) match 'Good' 4-5 star Regular/Dividend (none AC), and 234 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Tata Liquid Reg-IDCWD bought as one lumpsum of Rs 5,00,000 (2.7% of the account's portfolio) on label 89659236 (Ashutosh Gupta). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1395,19 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Liquid funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Liquid funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Liquid fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -1500,10 +1427,6 @@
           <t>Liquid</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1524,8 +1447,6 @@
           <t>89658587</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Navi Liquid Direct-G</t>
@@ -1551,7 +1472,6 @@
           <t>Sourav Adhikari</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1569,10 +1489,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1593,8 +1509,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>HDFC Short Term Direct-G</t>
@@ -1620,7 +1534,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1638,10 +1551,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1662,8 +1571,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>HDFC Short Term Direct-G</t>
@@ -1689,7 +1596,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1707,10 +1613,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1731,8 +1633,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>HDFC Short Term Direct-G</t>
@@ -1758,7 +1658,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1776,10 +1675,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1800,8 +1695,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>HDFC Short Term Direct-G</t>
@@ -1827,7 +1720,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1845,32 +1737,44 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>87684770</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>81844545</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>89661758</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ICICI Pru Short Term-G</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=ZDI0ZmNjZmEtYjY0ZS0xMWYxLThmOTItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>NOT FOUND: 4 Short Duration fund plan(s) match Analyst's Choice (Regular plan, not Direct-Growth), and 221 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: ICICI Pru Short Term-G bought as one lumpsum of Rs 1,50,000 (6.3% of the account's portfolio) on label 89661758 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -1890,10 +1794,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1914,8 +1814,6 @@
           <t>89659169</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Nippon India Short Term Direct-G</t>
@@ -1941,7 +1839,6 @@
           <t>Dwaraknath Krishnamurthi</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1959,10 +1856,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -1983,8 +1876,6 @@
           <t>89659169</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Nippon India Short Term Direct-G</t>
@@ -2010,7 +1901,6 @@
           <t>Dwaraknath Krishnamurthi</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2028,32 +1918,44 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>87681437</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>81843640</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>89659274</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Nippon India Short Term-G</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=MTZjMTQ4MjYtODMyMS0xMWYwLWE5YmItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>NOT FOUND: 28 Short Duration fund plan(s) match 'Good' 4-5 star Regular/Dividend (none AC), and 38 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Nippon India Short Term-G bought as one lumpsum of Rs 1,50,000 (7.5% of the account's portfolio) on label 89659274 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2073,32 +1975,19 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Short Duration funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Short Term (Short Duration) funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Short Duration fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -2118,32 +2007,19 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Short Duration funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Short Term (Short Duration) funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Short Duration fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -2163,10 +2039,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2177,14 +2049,16 @@
           <t>87680860</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>81593641</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>89658606</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>DSP Short Term Direct-G</t>
@@ -2210,7 +2084,6 @@
           <t>Ritesh</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2228,32 +2101,44 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87684770</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>81844545</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>89661758</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ICICI Pru Short Term-G</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=ZDI0ZmNjZmEtYjY0ZS0xMWYxLThmOTItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>NOT FOUND: 4 Short Duration fund plan(s) match Analyst's Choice (Regular plan, not Direct-Growth), and 221 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: ICICI Pru Short Term-G bought as one lumpsum of Rs 1,50,000 (6.3% of the account's portfolio) on label 89661758 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2273,10 +2158,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2297,8 +2178,6 @@
           <t>89659169</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Nippon India Short Term Direct-G</t>
@@ -2324,7 +2203,6 @@
           <t>Dwaraknath Krishnamurthi</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2342,32 +2220,44 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>87681437</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>81843640</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>89659274</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Nippon India Short Term-G</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=MTZjMTQ4MjYtODMyMS0xMWYwLWE5YmItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>NOT FOUND: 28 Short Duration fund plan(s) match 'Good' 4-5 star Regular/Dividend (none AC), and 38 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Nippon India Short Term-G bought as one lumpsum of Rs 1,50,000 (7.5% of the account's portfolio) on label 89659274 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2387,32 +2277,19 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): Short Duration funds in the opinion data are only 'Good' at 4-5 stars, so there is no 'Good' 1-3 star (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. Short Term (Short Duration) funds are rated 'Good' only at 4-5 stars in the opinion data, so there is no 'Good' 1-3 star Short Duration fund that an account could hold.</t>
         </is>
       </c>
     </row>
@@ -2432,10 +2309,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2446,14 +2319,16 @@
           <t>87680860</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>81593641</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>89658606</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>DSP Short Term Direct-G</t>
@@ -2479,7 +2354,6 @@
           <t>Ritesh</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2497,10 +2371,6 @@
           <t>Short Duration</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2511,14 +2381,16 @@
           <t>87680860</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>81593641</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>89658606</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>DSP Short Term Direct-G</t>
@@ -2544,7 +2416,6 @@
           <t>Ritesh</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2562,10 +2433,6 @@
           <t>Conservative Hybrid</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2586,8 +2453,6 @@
           <t>89659115</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Aditya Birla SL Conservative Hybrid Direct-G</t>
@@ -2613,7 +2478,6 @@
           <t>Srinivas Rao Koti</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2631,10 +2495,6 @@
           <t>Conservative Hybrid</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2655,8 +2515,6 @@
           <t>89659108</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Aditya Birla SL Conservative Hybrid Reg-IDCWM</t>
@@ -2682,7 +2540,6 @@
           <t>Jisha Chandanaparambil Usman</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2700,32 +2557,44 @@
           <t>Conservative Hybrid</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>87680912</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>55965691</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>89658660</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Baroda BNP Paribas Conservative Hybrid Reg-G</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=MGRlMjBhYzItNmQzYS00NDBjLTllZWUtODNlMzczZjk0Yzhm</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>NOT FOUND: 12 Conservative Hybrid fund plan(s) match 'Good' 1-3 star (none AC), and 7 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Baroda BNP Paribas Conservative Hybrid Reg-G bought as one lumpsum of Rs 50,000 (5.1% of the account's portfolio) on label 89658660 (Arpit Srivastava). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2745,10 +2614,6 @@
           <t>Conservative Hybrid</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2769,8 +2634,6 @@
           <t>89658889</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Kotak Conservative Hybrid Direct-G</t>
@@ -2796,7 +2659,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2814,10 +2676,6 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2838,8 +2696,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Mirae Asset Equity Savings Direct-G</t>
@@ -2865,7 +2721,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2883,32 +2738,44 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>87681399</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>81843632</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>89659236</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Kotak Equity Savings Reg-G</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=OWFiMzBlMzAtODE5Yi0xMWYwLWJmZWYtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>NOT FOUND: 3 Equity Savings fund plan(s) match Analyst's Choice (Regular plan, not Direct-Growth), and 71 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Kotak Equity Savings Reg-G bought as one lumpsum of Rs 5,00,000 (2.7% of the account's portfolio) on label 89659236 (Ashutosh Gupta). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2928,32 +2795,44 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>87684770</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>81844545</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>89661758</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Bandhan Equity Savings Direct-G</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=ZDI0ZmNjZmEtYjY0ZS0xMWYxLThmOTItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>NOT FOUND: 5 Equity Savings fund plan(s) match 'Good' 4-5 star Direct-Growth (none AC), and 154 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Bandhan Equity Savings Direct-G bought as one lumpsum of Rs 1,50,000 (6.3% of the account's portfolio) on label 89661758 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -2973,10 +2852,6 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -2997,8 +2872,6 @@
           <t>89659110</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>ICICI Pru Equity Savings-G</t>
@@ -3024,7 +2897,6 @@
           <t>Mansoor Kalathinal Pakkar</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3042,10 +2914,6 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3066,8 +2934,6 @@
           <t>89658587</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Axis Equity Savings Direct-G</t>
@@ -3093,7 +2959,6 @@
           <t>Sourav Adhikari</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3111,32 +2976,44 @@
           <t>Equity Savings</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>87681437</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>81843640</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>89659274</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Franklin India Equity Savings Reg-G</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=MTZjMTQ4MjYtODMyMS0xMWYwLWE5YmItMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>NOT FOUND: 36 Equity Savings fund plan(s) match neither 'Good' nor Analyst's Choice, and 42 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Franklin India Equity Savings Reg-G bought as one lumpsum of Rs 50,000 (2.5% of the account's portfolio) on label 89659274 (Sneha Suri). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -3156,10 +3033,6 @@
           <t>Dynamic Asset Allocation</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3180,8 +3053,6 @@
           <t>89658505</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>HDFC Balanced Advantage Direct-G</t>
@@ -3207,7 +3078,6 @@
           <t>Hemant Singh</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3225,10 +3095,6 @@
           <t>Dynamic Asset Allocation</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3249,8 +3115,6 @@
           <t>89657995</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>HDFC Balanced Advantage Reg-G</t>
@@ -3276,7 +3140,6 @@
           <t>Hemant Singh</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3294,10 +3157,6 @@
           <t>Dynamic Asset Allocation</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3318,8 +3177,6 @@
           <t>89659115</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Edelweiss Balanced Advantage Direct-G</t>
@@ -3345,7 +3202,6 @@
           <t>Srinivas Rao Koti</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3363,10 +3219,6 @@
           <t>Dynamic Asset Allocation</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3387,8 +3239,6 @@
           <t>89659144</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>ICICI Pru Dynamic Asset Allocation Active FoF Direct-G</t>
@@ -3414,7 +3264,6 @@
           <t>Ratan Bagrodia</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3432,10 +3281,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3456,8 +3301,6 @@
           <t>89657388</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>ICICI Pru Aggressive Hybrid Direct-G</t>
@@ -3483,7 +3326,6 @@
           <t>Dhirendra Kumar Jaiswal</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3501,10 +3343,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3525,8 +3363,6 @@
           <t>89660235</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Mirae Asset Aggressive Hybrid Reg-G</t>
@@ -3552,7 +3388,6 @@
           <t>Aakriti Shroff</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3570,10 +3405,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3594,8 +3425,6 @@
           <t>89658587</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Navi Aggressive Hybrid Direct-G</t>
@@ -3621,7 +3450,6 @@
           <t>Sourav Adhikari</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3639,10 +3467,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3663,8 +3487,6 @@
           <t>89658587</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Navi Aggressive Hybrid Direct-G</t>
@@ -3690,7 +3512,6 @@
           <t>Sourav Adhikari</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3708,10 +3529,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3732,8 +3549,6 @@
           <t>89660234</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>SBI Aggressive Hybrid-G</t>
@@ -3759,7 +3574,6 @@
           <t>Neela Yogesh Bhatt</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3777,10 +3591,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3801,8 +3611,6 @@
           <t>89659229</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Tata Retirement Savings Moderate Reg-G</t>
@@ -3828,7 +3636,6 @@
           <t>Paresh Jain</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3846,10 +3653,6 @@
           <t>Aggressive Hybrid</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3870,8 +3673,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>HDFC Aggressive Hybrid Direct-G</t>
@@ -3897,7 +3698,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3915,10 +3715,6 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -3939,8 +3735,6 @@
           <t>89657995</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Navi Nifty 50 Index Direct-G</t>
@@ -3966,7 +3760,6 @@
           <t>Hemant Singh</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3984,32 +3777,44 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>87680912</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>55965691</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>89658660</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>UTI Nifty 50 Index Reg-G</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=MGRlMjBhYzItNmQzYS00NDBjLTllZWUtODNlMzczZjk0Yzhm</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>NOT FOUND: 2 Nifty 50 index funds fund plan(s) match Analyst's Choice (Regular plan, not Direct-Growth), and 148 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: UTI Nifty 50 Index Reg-G bought as one lumpsum of Rs 50,000 (5.1% of the account's portfolio) on label 89658660 (Arpit Srivastava). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -4029,32 +3834,19 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): no Nifty 50 index fund has a 'Good' opinion with 4-5 stars, so there is no 'Good' 4-5 star Direct-Growth (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. No Nifty 50 index fund has a 'Good' opinion with 4-5 stars (Direct-Growth) in the opinion data, so no account can hold one.</t>
         </is>
       </c>
     </row>
@@ -4074,32 +3866,19 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>NOT_FOUND</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>NOT FOUND (cannot exist): no Nifty 50 index fund has a 'Good' opinion with 4-5 stars, so there is no 'Good' 4-5 star Regular/Dividend (none AC) fund to hold.</t>
+          <t>Dev 22-Oct: No account possible. No such fund exists. No Nifty 50 index fund has a 'Good' opinion with 4-5 stars (Regular/Dividend) in the opinion data, so no account can hold one.</t>
         </is>
       </c>
     </row>
@@ -4119,10 +3898,6 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4143,8 +3918,6 @@
           <t>89658724</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>ICICI Pru Nifty 50 Index Direct-G</t>
@@ -4170,7 +3943,6 @@
           <t>Nidhi Patel</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4188,10 +3960,6 @@
           <t>Nifty 50 index funds</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4212,8 +3980,6 @@
           <t>89659144</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>HDFC NIFTY 50 Index Direct-G</t>
@@ -4239,7 +4005,6 @@
           <t>Ratan Bagrodia</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4257,10 +4022,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4281,8 +4042,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -4308,7 +4067,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4326,10 +4084,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4350,8 +4104,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -4377,7 +4129,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4395,10 +4146,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4419,8 +4166,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -4446,7 +4191,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4464,10 +4208,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4488,8 +4228,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -4515,7 +4253,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4533,10 +4270,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4557,8 +4290,6 @@
           <t>89659173</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G; Kotak Large &amp; Mid Cap Direct-G; Franklin India Flexi Cap Direct-G</t>
@@ -4584,7 +4315,6 @@
           <t>Chintan Jyotindra Panchal</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4602,10 +4332,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4626,8 +4352,6 @@
           <t>89658894</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Reg-G</t>
@@ -4653,7 +4377,6 @@
           <t>Nitin Kashyap</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4671,10 +4394,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4695,8 +4414,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>ICICI Pru Focused Direct-G</t>
@@ -4722,7 +4439,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4740,10 +4456,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4764,8 +4476,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -4791,7 +4501,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4809,10 +4518,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4833,8 +4538,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -4860,7 +4563,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4878,10 +4580,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4902,8 +4600,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -4929,7 +4625,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4947,10 +4642,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -4971,8 +4662,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -4998,7 +4687,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5016,10 +4704,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5040,8 +4724,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -5067,7 +4749,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5085,10 +4766,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5109,8 +4786,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -5136,7 +4811,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5154,10 +4828,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5178,8 +4848,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -5205,7 +4873,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5223,10 +4890,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5247,8 +4910,6 @@
           <t>89659173</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G; Kotak Large &amp; Mid Cap Direct-G; Franklin India Flexi Cap Direct-G</t>
@@ -5274,7 +4935,6 @@
           <t>Chintan Jyotindra Panchal</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5292,10 +4952,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5316,8 +4972,6 @@
           <t>89658894</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Reg-G</t>
@@ -5343,7 +4997,6 @@
           <t>Nitin Kashyap</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5361,10 +5014,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5385,8 +5034,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>ICICI Pru Focused Direct-G</t>
@@ -5412,7 +5059,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5430,10 +5076,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5454,8 +5096,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -5481,7 +5121,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5499,10 +5138,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5523,8 +5158,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -5550,7 +5183,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5568,10 +5200,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5592,8 +5220,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -5619,7 +5245,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5637,10 +5262,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5661,8 +5282,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -5688,7 +5307,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5706,10 +5324,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5730,8 +5344,6 @@
           <t>89659173</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G; Kotak Large &amp; Mid Cap Direct-G; Franklin India Flexi Cap Direct-G</t>
@@ -5757,7 +5369,6 @@
           <t>Chintan Jyotindra Panchal</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5775,10 +5386,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5799,8 +5406,6 @@
           <t>89658894</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Reg-G</t>
@@ -5826,7 +5431,6 @@
           <t>Nitin Kashyap</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5844,10 +5448,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5868,8 +5468,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>ICICI Pru Focused Direct-G</t>
@@ -5895,7 +5493,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5913,10 +5510,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -5937,8 +5530,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -5964,7 +5555,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5982,10 +5572,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6006,8 +5592,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -6033,7 +5617,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6051,10 +5634,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6075,8 +5654,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -6102,7 +5679,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6120,10 +5696,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6144,8 +5716,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -6171,7 +5741,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6189,10 +5758,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6213,8 +5778,6 @@
           <t>89659173</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G; Kotak Large &amp; Mid Cap Direct-G; Franklin India Flexi Cap Direct-G</t>
@@ -6240,7 +5803,6 @@
           <t>Chintan Jyotindra Panchal</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6258,10 +5820,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6282,8 +5840,6 @@
           <t>89658894</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Reg-G</t>
@@ -6309,7 +5865,6 @@
           <t>Nitin Kashyap</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6327,10 +5882,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6351,8 +5902,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>ICICI Pru Focused Direct-G</t>
@@ -6378,7 +5927,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6396,10 +5944,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6420,8 +5964,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -6447,7 +5989,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6465,10 +6006,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6489,8 +6026,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -6516,7 +6051,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6534,10 +6068,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6558,8 +6088,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -6585,7 +6113,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6603,10 +6130,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6627,8 +6150,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G</t>
@@ -6654,7 +6175,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6672,10 +6192,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6696,8 +6212,6 @@
           <t>89659173</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Direct-G; Kotak Large &amp; Mid Cap Direct-G; Franklin India Flexi Cap Direct-G</t>
@@ -6723,7 +6237,6 @@
           <t>Chintan Jyotindra Panchal</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6741,10 +6254,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6765,8 +6274,6 @@
           <t>89658894</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>Parag Parikh Flexi Cap Reg-G</t>
@@ -6792,7 +6299,6 @@
           <t>Nitin Kashyap</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6810,10 +6316,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6834,8 +6336,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>ICICI Pru Focused Direct-G</t>
@@ -6861,7 +6361,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6879,10 +6378,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6903,8 +6398,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>HDFC Large &amp; Mid Cap Reg-G</t>
@@ -6930,7 +6423,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6948,10 +6440,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -6972,8 +6460,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>Axis Flexi Cap Direct-G</t>
@@ -6999,7 +6485,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7017,10 +6502,6 @@
           <t>Flexicap/Multicap/Large &amp; Mid cap/Focused</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7041,8 +6522,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>Navi Flexi Cap Direct-G</t>
@@ -7068,7 +6547,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7086,10 +6564,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7110,8 +6584,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>SBI Contra Direct-G</t>
@@ -7137,7 +6609,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7155,10 +6626,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7179,8 +6646,6 @@
           <t>89659206</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>Invesco India Contra Reg-G</t>
@@ -7206,7 +6671,6 @@
           <t>Surbhi Chugh</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7224,10 +6688,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7248,8 +6708,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>Kotak Contra Direct-G</t>
@@ -7275,7 +6733,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7293,10 +6750,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7317,8 +6770,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>Nippon India Value-G</t>
@@ -7344,7 +6795,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7362,10 +6812,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7386,8 +6832,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>Tata Value Direct-G</t>
@@ -7413,7 +6857,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7431,32 +6874,44 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>87681450</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>81843651</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>89659282</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Templeton India Value-G</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=NDdmZmJkNTAtODU5Yy0xMWYwLWE3NWEtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>NOT FOUND: 83 Value fund plan(s) match neither 'Good' nor Analyst's Choice, and 657 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Templeton India Value-G bought as one lumpsum of Rs 25,000 (8.9% of the account's portfolio) on label 89659282 (Gaurav Singh). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -7476,10 +6931,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7500,8 +6951,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>SBI Contra Direct-G</t>
@@ -7527,7 +6976,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7545,10 +6993,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7569,8 +7013,6 @@
           <t>89659206</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>Invesco India Contra Reg-G</t>
@@ -7596,7 +7038,6 @@
           <t>Surbhi Chugh</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7614,10 +7055,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7638,8 +7075,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>Kotak Contra Direct-G</t>
@@ -7665,7 +7100,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7683,10 +7117,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7707,8 +7137,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>Nippon India Value-G</t>
@@ -7734,7 +7162,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7752,10 +7179,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7776,8 +7199,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>Tata Value Direct-G</t>
@@ -7803,7 +7224,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7821,32 +7241,44 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>87681450</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>81843651</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>89659282</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Templeton India Value-G</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=NDdmZmJkNTAtODU5Yy0xMWYwLWE3NWEtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
-          <t>NOT FOUND: 83 Value fund plan(s) match neither 'Good' nor Analyst's Choice, and 657 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Templeton India Value-G bought as one lumpsum of Rs 25,000 (8.9% of the account's portfolio) on label 89659282 (Gaurav Singh). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -7866,10 +7298,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7890,8 +7318,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>SBI Contra Direct-G</t>
@@ -7917,7 +7343,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7935,10 +7360,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -7959,8 +7380,6 @@
           <t>89659206</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>Invesco India Contra Reg-G</t>
@@ -7986,7 +7405,6 @@
           <t>Surbhi Chugh</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8004,10 +7422,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8028,8 +7442,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>Kotak Contra Direct-G</t>
@@ -8055,7 +7467,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8073,10 +7484,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8097,8 +7504,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>Nippon India Value-G</t>
@@ -8124,7 +7529,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8142,10 +7546,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8166,8 +7566,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>Tata Value Direct-G</t>
@@ -8193,7 +7591,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8211,32 +7608,44 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>87681450</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>81843651</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>89659282</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Templeton India Value-G</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=NDdmZmJkNTAtODU5Yy0xMWYwLWE3NWEtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
-          <t>NOT FOUND: 83 Value fund plan(s) match neither 'Good' nor Analyst's Choice, and 657 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Templeton India Value-G bought as one lumpsum of Rs 25,000 (8.9% of the account's portfolio) on label 89659282 (Gaurav Singh). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -8256,10 +7665,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8280,8 +7685,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>SBI Contra Direct-G</t>
@@ -8307,7 +7710,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8325,10 +7727,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8349,8 +7747,6 @@
           <t>89659206</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>Invesco India Contra Reg-G</t>
@@ -8376,7 +7772,6 @@
           <t>Surbhi Chugh</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8394,10 +7789,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8418,8 +7809,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>Kotak Contra Direct-G</t>
@@ -8445,7 +7834,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8463,10 +7851,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8487,8 +7871,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>Nippon India Value-G</t>
@@ -8514,7 +7896,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8532,10 +7913,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8556,8 +7933,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>Tata Value Direct-G</t>
@@ -8583,7 +7958,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8601,32 +7975,44 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>87681450</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>81843651</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>89659282</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Templeton India Value-G</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=NDdmZmJkNTAtODU5Yy0xMWYwLWE3NWEtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
-          <t>NOT FOUND: 83 Value fund plan(s) match neither 'Good' nor Analyst's Choice, and 657 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Templeton India Value-G bought as one lumpsum of Rs 25,000 (8.9% of the account's portfolio) on label 89659282 (Gaurav Singh). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -8646,10 +8032,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8670,8 +8052,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>SBI Contra Direct-G</t>
@@ -8697,7 +8077,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8715,10 +8094,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8739,8 +8114,6 @@
           <t>89659206</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>Invesco India Contra Reg-G</t>
@@ -8766,7 +8139,6 @@
           <t>Surbhi Chugh</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8784,10 +8156,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8808,8 +8176,6 @@
           <t>89659178</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>Kotak Contra Direct-G</t>
@@ -8835,7 +8201,6 @@
           <t>Krupa Chintan Panchal</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8853,10 +8218,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8877,8 +8238,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>Nippon India Value-G</t>
@@ -8904,7 +8263,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8922,10 +8280,6 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -8946,8 +8300,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>Tata Value Direct-G</t>
@@ -8973,7 +8325,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8991,32 +8342,44 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+          <t>ACTIVE_MATCH_FOUND</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>87681450</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>81843651</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>89659282</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Templeton India Value-G</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>https://uat2.valueresearchonline.com/login-by-guid/?guid=NDdmZmJkNTAtODU5Yy0xMWYwLWE3NWEtMDAxNjNlNWM0ZmMy</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
-          <t>NOT FOUND: 83 Value fund plan(s) match neither 'Good' nor Analyst's Choice, and 657 label(s) hold them, but none of those labels is verified. A verified, onboarded label with this holding is needed.</t>
+          <t>Dev 22-Oct: New account added: Templeton India Value-G bought as one lumpsum of Rs 25,000 (8.9% of the account's portfolio) on label 89659282 (Gaurav Singh). Account is verified, onboarded and subscribed; risk profile matches the case.</t>
         </is>
       </c>
     </row>
@@ -9036,10 +8399,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9060,8 +8419,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>Kotak Mid Cap Direct-G</t>
@@ -9087,7 +8444,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9105,10 +8461,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9129,8 +8481,6 @@
           <t>89659243</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>Edelweiss Mid Cap Reg-G</t>
@@ -9156,7 +8506,6 @@
           <t>Sneha Suri</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9174,10 +8523,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9198,8 +8543,6 @@
           <t>89657388</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>Nippon India Growth Mid Cap Direct-G</t>
@@ -9225,7 +8568,6 @@
           <t>Dhirendra Kumar Jaiswal</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9243,10 +8585,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9267,8 +8605,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>HDFC Mid Cap Reg-G</t>
@@ -9294,7 +8630,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9312,10 +8647,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9336,8 +8667,6 @@
           <t>89658362</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>Aditya Birla SL Nifty Midcap 150 Index Direct-G</t>
@@ -9363,7 +8692,6 @@
           <t>Amit Verma</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9381,10 +8709,6 @@
           <t>Mid Cap</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9405,8 +8729,6 @@
           <t>89659124</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>Motilal Oswal Midcap Direct-G</t>
@@ -9432,7 +8754,6 @@
           <t>Sriram Subramaniyan</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9450,10 +8771,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9474,8 +8791,6 @@
           <t>89660815</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>Bandhan Small Cap Direct-G</t>
@@ -9501,7 +8816,6 @@
           <t>Ajay Kumar Gupta</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9519,10 +8833,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9543,8 +8853,6 @@
           <t>89658640</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>Bandhan Small Cap Reg-G</t>
@@ -9570,7 +8878,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9588,10 +8895,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9612,8 +8915,6 @@
           <t>89659110</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>Nippon India Small Cap Direct-G</t>
@@ -9639,7 +8940,6 @@
           <t>Mansoor Kalathinal Pakkar</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9657,10 +8957,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9681,8 +8977,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>Nippon India Small Cap-G</t>
@@ -9708,7 +9002,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9726,10 +9019,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9750,8 +9039,6 @@
           <t>89659124</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>Quant Small Cap Direct-G</t>
@@ -9777,7 +9064,6 @@
           <t>Sriram Subramaniyan</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9795,10 +9081,6 @@
           <t>Small Cap</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9819,8 +9101,6 @@
           <t>89657847</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>Motilal Oswal Nifty Microcap 250 Index Direct-G</t>
@@ -9846,7 +9126,6 @@
           <t>Vikas Vardhan</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9864,10 +9143,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9888,8 +9163,6 @@
           <t>89658403</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>Parag Parikh ELSS Tax Saver Direct-G</t>
@@ -9915,7 +9188,6 @@
           <t>Gulnaz Parveen</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9933,10 +9205,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -9957,8 +9225,6 @@
           <t>89659208</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>HDFC ELSS - Tax Saver Reg-G</t>
@@ -9984,7 +9250,6 @@
           <t>Vimmi Chugh</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10002,10 +9267,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -10026,8 +9287,6 @@
           <t>89658852</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>Motilal Oswal ELSS Tax Saver Direct-G</t>
@@ -10053,7 +9312,6 @@
           <t>Ruchira Sharma</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10071,10 +9329,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -10095,8 +9349,6 @@
           <t>89659169</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>HSBC ELSS Tax Saver-G</t>
@@ -10122,7 +9374,6 @@
           <t>Dwaraknath Krishnamurthi</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10140,10 +9391,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -10164,8 +9411,6 @@
           <t>89659124</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>Invesco India ELSS Tax Saver Reg-IDCW</t>
@@ -10191,7 +9436,6 @@
           <t>Sriram Subramaniyan</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10209,10 +9453,6 @@
           <t>ELSS</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>ACTIVE_MATCH_FOUND</t>
@@ -10233,8 +9473,6 @@
           <t>89659131</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>Axis ELSS - Tax Saver Direct-G</t>
@@ -10260,7 +9498,6 @@
           <t>Gagandeep Kaur</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10445,13 +9682,16 @@
       <c r="N3" t="n">
         <v>2</v>
       </c>
+      <c r="O3" t="n">
+        <v>35000</v>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -10492,13 +9732,16 @@
       <c r="N4" t="n">
         <v>2</v>
       </c>
+      <c r="O4" t="n">
+        <v>15000</v>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -10539,13 +9782,16 @@
       <c r="N5" t="n">
         <v>2</v>
       </c>
+      <c r="O5" t="n">
+        <v>75000</v>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -10688,13 +9934,16 @@
       <c r="N9" t="n">
         <v>2</v>
       </c>
+      <c r="O9" t="n">
+        <v>35000</v>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -10769,13 +10018,16 @@
       <c r="N11" t="n">
         <v>2</v>
       </c>
+      <c r="O11" t="n">
+        <v>35000</v>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -11088,13 +10340,16 @@
       <c r="N20" t="n">
         <v>2</v>
       </c>
+      <c r="O20" t="n">
+        <v>35000</v>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -11140,7 +10395,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -11185,16 +10440,13 @@
       <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="O22" t="n">
-        <v>75000</v>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -11303,13 +10555,16 @@
       <c r="N25" t="n">
         <v>2</v>
       </c>
+      <c r="O25" t="n">
+        <v>35000</v>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -11418,16 +10673,13 @@
       <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="O28" t="n">
-        <v>35000</v>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -12284,13 +11536,16 @@
       <c r="N53" t="n">
         <v>2</v>
       </c>
+      <c r="O53" t="n">
+        <v>15000</v>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -12671,13 +11926,16 @@
       <c r="N64" t="n">
         <v>2</v>
       </c>
+      <c r="O64" t="n">
+        <v>35000</v>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -12718,13 +11976,16 @@
       <c r="N65" t="n">
         <v>2</v>
       </c>
+      <c r="O65" t="n">
+        <v>15000</v>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -12765,13 +12026,16 @@
       <c r="N66" t="n">
         <v>2</v>
       </c>
+      <c r="O66" t="n">
+        <v>75000</v>
+      </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -12919,7 +12183,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -13032,16 +12296,13 @@
       <c r="N73" t="n">
         <v>2</v>
       </c>
-      <c r="O73" t="n">
-        <v>35000</v>
-      </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -13116,16 +12377,13 @@
       <c r="N75" t="n">
         <v>2</v>
       </c>
-      <c r="O75" t="n">
-        <v>35000</v>
-      </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>App request (14-Oct): start_regular_income = Needed when (1/2/3); annual_income_range = 2; needed_annual_amount null for start 1, monthly income for 2/3</t>
+          <t>App payload (UAT DevTools, 22-Oct): start_regular_income Immediately=3, Next 1 year=2, Next 1-5 years=1; needed_annual_amount = monthly income (null for Next 1-5 years); annual_income_range = 2</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
